--- a/public/templates/process-docs/配电柜安装接地检查记录.xlsx
+++ b/public/templates/process-docs/配电柜安装接地检查记录.xlsx
@@ -135,13 +135,13 @@
     <t xml:space="preserve">总承包单位</t>
   </si>
   <si>
-    <t xml:space="preserve">中核华辰建筑工程有限公司</t>
+    <t xml:space="preserve">{{施工单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">项目负责人</t>
   </si>
   <si>
-    <t xml:space="preserve">谢智敏</t>
+    <t xml:space="preserve">{{施工单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">施工执行标准名称及编号</t>
